--- a/mergedata/doc/门诊现金总统计表.xlsx
+++ b/mergedata/doc/门诊现金总统计表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86156\Desktop\门诊现金统计表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC2BC87-B0C2-4E5A-A08B-C8186C1477B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20051774-0199-4095-A49E-E5BD19C413E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -268,15 +268,6 @@
     <t>门诊当日回款</t>
   </si>
   <si>
-    <t>门诊当日抵扣报表金额</t>
-  </si>
-  <si>
-    <t>门诊当日退主病房</t>
-  </si>
-  <si>
-    <t>门诊当日退三住院部</t>
-  </si>
-  <si>
     <t>门诊当日实存金额</t>
   </si>
   <si>
@@ -379,15 +370,28 @@
     <t>1、标记绿色的标题列可修改，即可手工输入数字，2、如果是周五（节假日前一天）{实交报表数③=①-②-④}，如果是周一（节假日正常工作日当天）{实交报表数③=①-④(周五)-sum(X)(周五+周六+周末)}，周六周日{实交报表数③=①-x)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>门诊当日抵扣报表金额</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>门诊当日退主病房</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>门诊当日退三住院部</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -454,6 +458,14 @@
       <family val="1"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -475,7 +487,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -529,13 +541,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -557,9 +609,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -575,26 +624,59 @@
     <xf numFmtId="176" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1086,29 +1168,29 @@
     <col min="17" max="16384" width="20.6640625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="15" customFormat="1" ht="125.4" customHeight="1">
-      <c r="A1" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="88.95" customHeight="1">
-      <c r="A2" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
+    <row r="1" spans="1:15" s="17" customFormat="1" ht="108" customHeight="1">
+      <c r="A1" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="52.2" customHeight="1">
+      <c r="A2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
     </row>
     <row r="3" spans="1:15" ht="30" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -1117,10 +1199,10 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -1133,13 +1215,13 @@
         <v>7</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>46</v>
+        <v>41</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>8</v>
@@ -1150,7 +1232,7 @@
       <c r="M3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="1" t="s">
@@ -1164,43 +1246,43 @@
       <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>1</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>2</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11">
+      <c r="E4" s="10"/>
+      <c r="F4" s="10">
         <f>C4+D4+E4</f>
         <v>3</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <v>2</v>
       </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11">
+      <c r="H4" s="10"/>
+      <c r="I4" s="10">
         <f>F4-G4</f>
         <v>1</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="10">
         <v>5</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="10">
         <f>I4+J4</f>
         <v>6</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="10">
         <f>M4-I4-N4</f>
         <v>-1</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M4" s="10">
         <v>5000</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="10">
         <v>5000</v>
       </c>
-      <c r="O4" s="11"/>
+      <c r="O4" s="10"/>
     </row>
     <row r="5" spans="1:15" ht="30" customHeight="1">
       <c r="A5" s="1">
@@ -1209,31 +1291,31 @@
       <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11">
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10">
         <f t="shared" ref="F5:F21" si="0">C5+D5+E5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11">
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10">
         <f t="shared" ref="I5:I20" si="1">F5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11">
+      <c r="J5" s="10"/>
+      <c r="K5" s="10">
         <f t="shared" ref="K5:K20" si="2">I5+J5</f>
         <v>0</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="10">
         <f t="shared" ref="L5:L20" si="3">M5-I5-N5</f>
         <v>0</v>
       </c>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
       <c r="A6" s="1">
@@ -1242,31 +1324,31 @@
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11">
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11">
+      <c r="J6" s="10"/>
+      <c r="K6" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
     </row>
     <row r="7" spans="1:15" ht="30" customHeight="1">
       <c r="A7" s="1">
@@ -1275,31 +1357,31 @@
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11">
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11">
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11">
+      <c r="J7" s="10"/>
+      <c r="K7" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
     </row>
     <row r="8" spans="1:15" ht="30" customHeight="1">
       <c r="A8" s="1">
@@ -1308,31 +1390,31 @@
       <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11">
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11">
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11">
+      <c r="J8" s="10"/>
+      <c r="K8" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
     </row>
     <row r="9" spans="1:15" ht="30" customHeight="1">
       <c r="A9" s="1">
@@ -1341,33 +1423,33 @@
       <c r="B9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11">
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11">
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="10">
         <v>3</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="10">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="L9" s="11">
+      <c r="L9" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
     </row>
     <row r="10" spans="1:15" ht="30" customHeight="1">
       <c r="A10" s="1">
@@ -1376,31 +1458,31 @@
       <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11">
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11">
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11">
+      <c r="J10" s="10"/>
+      <c r="K10" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L10" s="11">
+      <c r="L10" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
     </row>
     <row r="11" spans="1:15" ht="30" customHeight="1">
       <c r="A11" s="1">
@@ -1409,33 +1491,33 @@
       <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <v>3</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11">
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11">
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11">
+      <c r="J11" s="10"/>
+      <c r="K11" s="10">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="10">
         <f t="shared" si="3"/>
         <v>-3</v>
       </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
     </row>
     <row r="12" spans="1:15" ht="30" customHeight="1">
       <c r="A12" s="1">
@@ -1444,36 +1526,36 @@
       <c r="B12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11">
+      <c r="C12" s="10"/>
+      <c r="D12" s="10">
         <v>6</v>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11">
+      <c r="E12" s="10"/>
+      <c r="F12" s="10">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11">
+      <c r="G12" s="10"/>
+      <c r="H12" s="10">
         <v>34</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="10">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11">
+      <c r="J12" s="10"/>
+      <c r="K12" s="10">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="10">
         <v>400</v>
       </c>
-      <c r="M12" s="11">
+      <c r="M12" s="10">
         <v>700</v>
       </c>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
     </row>
     <row r="13" spans="1:15" ht="30" customHeight="1">
       <c r="A13" s="1">
@@ -1482,35 +1564,35 @@
       <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11">
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11">
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11">
+      <c r="J13" s="10"/>
+      <c r="K13" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="10">
         <f t="shared" si="3"/>
         <v>500</v>
       </c>
-      <c r="M13" s="11">
+      <c r="M13" s="10">
         <v>600</v>
       </c>
-      <c r="N13" s="11">
+      <c r="N13" s="10">
         <v>100</v>
       </c>
-      <c r="O13" s="11"/>
+      <c r="O13" s="10"/>
     </row>
     <row r="14" spans="1:15" ht="30" customHeight="1">
       <c r="A14" s="1">
@@ -1519,37 +1601,37 @@
       <c r="B14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11">
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11">
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="10">
         <v>4</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="10">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="10">
         <f t="shared" si="3"/>
         <v>-100</v>
       </c>
-      <c r="M14" s="11">
+      <c r="M14" s="10">
         <v>700</v>
       </c>
-      <c r="N14" s="11">
+      <c r="N14" s="10">
         <v>800</v>
       </c>
-      <c r="O14" s="11"/>
+      <c r="O14" s="10"/>
     </row>
     <row r="15" spans="1:15" ht="30" customHeight="1">
       <c r="A15" s="1">
@@ -1558,35 +1640,35 @@
       <c r="B15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11">
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10">
         <v>2</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="10">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11">
+      <c r="G15" s="10"/>
+      <c r="H15" s="10">
         <v>43</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="10">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11">
+      <c r="J15" s="10"/>
+      <c r="K15" s="10">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L15" s="11">
+      <c r="L15" s="10">
         <f t="shared" si="3"/>
         <v>-2</v>
       </c>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
     </row>
     <row r="16" spans="1:15" ht="30" customHeight="1">
       <c r="A16" s="1">
@@ -1595,39 +1677,39 @@
       <c r="B16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <v>3</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <v>1</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="10">
         <v>2</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11">
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="10">
         <v>5</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="10">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="L16" s="11">
+      <c r="L16" s="10">
         <f t="shared" si="3"/>
         <v>-6</v>
       </c>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
     </row>
     <row r="17" spans="1:15" ht="30" customHeight="1">
       <c r="A17" s="1">
@@ -1636,37 +1718,37 @@
       <c r="B17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11">
+      <c r="C17" s="10"/>
+      <c r="D17" s="10">
         <v>2</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="10">
         <v>12</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="10">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11">
+      <c r="G17" s="10"/>
+      <c r="H17" s="10">
         <v>23</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="10">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11">
+      <c r="J17" s="10"/>
+      <c r="K17" s="10">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="10">
         <f t="shared" si="3"/>
         <v>-14</v>
       </c>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
     </row>
     <row r="18" spans="1:15" ht="30" customHeight="1">
       <c r="A18" s="1">
@@ -1675,37 +1757,37 @@
       <c r="B18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11">
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10">
         <v>23</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="10">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11">
+      <c r="G18" s="10"/>
+      <c r="H18" s="10">
         <v>43</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="10">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11">
+      <c r="J18" s="10"/>
+      <c r="K18" s="10">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="L18" s="11">
+      <c r="L18" s="10">
         <f t="shared" si="3"/>
         <v>877</v>
       </c>
-      <c r="M18" s="11">
+      <c r="M18" s="10">
         <v>900</v>
       </c>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
     </row>
     <row r="19" spans="1:15" ht="30" customHeight="1">
       <c r="A19" s="1">
@@ -1714,31 +1796,31 @@
       <c r="B19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11">
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11">
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11">
+      <c r="J19" s="10"/>
+      <c r="K19" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="11">
+      <c r="L19" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
     </row>
     <row r="20" spans="1:15" ht="30" customHeight="1">
       <c r="A20" s="1">
@@ -1747,93 +1829,96 @@
       <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11">
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11">
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11">
+      <c r="J20" s="10"/>
+      <c r="K20" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-    </row>
-    <row r="21" spans="1:15" s="19" customFormat="1" ht="30" customHeight="1">
-      <c r="A21" s="18" t="s">
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+    </row>
+    <row r="21" spans="1:15" s="13" customFormat="1" ht="30" customHeight="1">
+      <c r="A21" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="12">
+      <c r="B21" s="21"/>
+      <c r="C21" s="11">
         <f>SUM(C4:C20)</f>
         <v>7</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="11">
         <f t="shared" ref="D21:M21" si="4">SUM(D4:D20)</f>
         <v>11</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="11">
         <f t="shared" si="4"/>
         <v>39</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="12">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="11">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="11">
         <f t="shared" si="4"/>
         <v>143</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="11">
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21" s="11">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="11">
         <f t="shared" si="4"/>
         <v>72</v>
       </c>
-      <c r="L21" s="12">
+      <c r="L21" s="11">
         <f t="shared" si="4"/>
         <v>1651</v>
       </c>
-      <c r="M21" s="12">
+      <c r="M21" s="11">
         <f t="shared" si="4"/>
         <v>7900</v>
       </c>
-      <c r="N21" s="12">
+      <c r="N21" s="11">
         <f t="shared" ref="N21" si="5">SUM(N4:N20)</f>
         <v>5900</v>
       </c>
-      <c r="O21" s="17"/>
+      <c r="O21" s="12"/>
     </row>
     <row r="22" spans="1:15" ht="30" customHeight="1">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="1"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="10">
+        <f>J21</f>
+        <v>17</v>
+      </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1844,15 +1929,18 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="23"/>
     </row>
     <row r="23" spans="1:15" ht="30" customHeight="1">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="1"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="10">
+        <f>F21</f>
+        <v>57</v>
+      </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -1863,184 +1951,191 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="25"/>
     </row>
     <row r="24" spans="1:15" ht="30" customHeight="1">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
+      <c r="N24" s="24"/>
+      <c r="O24" s="25"/>
     </row>
     <row r="25" spans="1:15" ht="30" customHeight="1">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="25"/>
     </row>
     <row r="26" spans="1:15" ht="30" customHeight="1">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="28">
+        <v>20</v>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="25"/>
     </row>
     <row r="27" spans="1:15" ht="30" customHeight="1">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="28">
+        <v>2</v>
+      </c>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="25"/>
     </row>
     <row r="28" spans="1:15" ht="30" customHeight="1">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="1:15" ht="30" customHeight="1">
-      <c r="A29" s="13" t="s">
+      <c r="N28" s="24"/>
+      <c r="O28" s="25"/>
+    </row>
+    <row r="29" spans="1:15" s="15" customFormat="1" ht="30" customHeight="1">
+      <c r="A29" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="24"/>
+      <c r="O29" s="25"/>
+    </row>
+    <row r="30" spans="1:15" s="15" customFormat="1" ht="30" customHeight="1">
+      <c r="A30" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="24"/>
+      <c r="O30" s="25"/>
+    </row>
+    <row r="31" spans="1:15" s="15" customFormat="1" ht="30" customHeight="1">
+      <c r="A31" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="24"/>
+      <c r="O31" s="25"/>
+    </row>
+    <row r="32" spans="1:15" ht="30" customHeight="1">
+      <c r="A32" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="1:15" ht="30" customHeight="1">
-      <c r="A30" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="1:15" ht="30" customHeight="1">
-      <c r="A31" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="1:15" ht="30" customHeight="1">
-      <c r="A32" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="28">
+        <f>C22+C23+C24+C26+C28-C27-C25</f>
+        <v>92</v>
+      </c>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="27"/>
     </row>
     <row r="33" spans="1:15" ht="30" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -2052,7 +2147,7 @@
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
@@ -2061,7 +2156,13 @@
     <row r="34" spans="1:15" ht="16.8" customHeight="1"/>
     <row r="35" spans="1:15" ht="16.8" customHeight="1"/>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
     <mergeCell ref="A1:XFD1"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A29:B29"/>
@@ -2070,12 +2171,7 @@
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="N22:O32"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
